--- a/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0003T0006Z000C1N40_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0003T0006Z000C1N40_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>21.35915121895781</v>
+        <v>3.470862073080644</v>
       </c>
       <c r="D2" t="n">
-        <v>38.29649141129779</v>
+        <v>6.223179854335891</v>
       </c>
       <c r="E2" t="n">
-        <v>15.37420123623258</v>
+        <v>2.498307700887795</v>
       </c>
       <c r="F2" t="n">
-        <v>15.47212329128939</v>
+        <v>2.514220034834526</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>30.00944853407563</v>
+        <v>4.87653538678729</v>
       </c>
       <c r="D3" t="n">
-        <v>16.47181919095533</v>
+        <v>2.676670618530241</v>
       </c>
       <c r="E3" t="n">
-        <v>15.37420123623258</v>
+        <v>2.498307700887795</v>
       </c>
       <c r="F3" t="n">
-        <v>15.47212329128939</v>
+        <v>2.514220034834526</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>49.32646358798513</v>
+        <v>8.015550333047583</v>
       </c>
       <c r="D4" t="n">
-        <v>41.85824374334067</v>
+        <v>6.80196460829286</v>
       </c>
       <c r="E4" t="n">
-        <v>15.37420123623258</v>
+        <v>2.498307700887795</v>
       </c>
       <c r="F4" t="n">
-        <v>15.47212329128939</v>
+        <v>2.514220034834526</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>7.441245512670394</v>
+        <v>1.209202395808939</v>
       </c>
       <c r="D5" t="n">
-        <v>2.248221728623774</v>
+        <v>0.3653360309013632</v>
       </c>
       <c r="E5" t="n">
-        <v>15.37420123623258</v>
+        <v>2.498307700887795</v>
       </c>
       <c r="F5" t="n">
-        <v>15.47212329128939</v>
+        <v>2.514220034834526</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>35.96396630563914</v>
+        <v>5.84414452466636</v>
       </c>
       <c r="D6" t="n">
-        <v>35.9790263817679</v>
+        <v>5.846591787037284</v>
       </c>
       <c r="E6" t="n">
-        <v>15.37420123623258</v>
+        <v>2.498307700887795</v>
       </c>
       <c r="F6" t="n">
-        <v>15.47212329128939</v>
+        <v>2.514220034834526</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>6.038091568939453</v>
+        <v>0.981189879952661</v>
       </c>
       <c r="D7" t="n">
-        <v>8.515526737932634</v>
+        <v>1.383773094914053</v>
       </c>
       <c r="E7" t="n">
-        <v>15.37420123623258</v>
+        <v>2.498307700887795</v>
       </c>
       <c r="F7" t="n">
-        <v>15.47212329128939</v>
+        <v>2.514220034834526</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
